--- a/shared/Test1.xlsx
+++ b/shared/Test1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="420" windowWidth="27555" windowHeight="12825"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="295">
   <si>
     <t>Bug</t>
   </si>
@@ -897,13 +897,12 @@
     <t>13/Jan/2023 8:53 AM;698877135425;SOF.png;/data/shared/SOF.png</t>
   </si>
   <si>
-    <t>13/Jan/2023 8:53 AM;698877135426;SOF.png;/data/shared/SOF-2.png</t>
-  </si>
-  <si>
-    <t>13/Jan/2023 8:53 AM;698877135426;SOF.png;/data/shared/T1.txt</t>
-  </si>
-  <si>
-    <t>13/Jan/2023 8:53 AM;698877135426;SOF.png;/data/shared/T1.pdf</t>
+    <t>Go to Sign Up. Enter email. Click 'Verify Email'. Wait for confirmation. I got the following error:  XHR finished loading: POST "/api/auth/verify-email" [pending - never resolves]
+No response received after 60s timeout
+Suspected: request hangs on SMTP server call with no timeout configured</t>
+  </si>
+  <si>
+    <t>Infinite loading spinner on account verification page</t>
   </si>
 </sst>
 </file>
@@ -939,11 +938,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,6 +955,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2768,7 +2773,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:491" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:491" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>271</v>
       </c>
@@ -2841,15 +2846,6 @@
       <c r="DT2" t="s">
         <v>292</v>
       </c>
-      <c r="DU2" t="s">
-        <v>293</v>
-      </c>
-      <c r="DV2" t="s">
-        <v>294</v>
-      </c>
-      <c r="DW2" t="s">
-        <v>295</v>
-      </c>
       <c r="EM2" t="s">
         <v>280</v>
       </c>
@@ -2935,11 +2931,29 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:491" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:491" ht="43.15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" t="s">
+        <v>6</v>
+      </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
+      <c r="BD3" s="4" t="s">
+        <v>293</v>
+      </c>
       <c r="EN3" s="2"/>
       <c r="ES3" s="2"/>
       <c r="FM3" s="3"/>
